--- a/src/ledger.xlsx
+++ b/src/ledger.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
